--- a/rules/CORE-001034/positive/01/data/unit-test-coreid-CG0562-positive 1.xlsx
+++ b/rules/CORE-001034/positive/01/data/unit-test-coreid-CG0562-positive 1.xlsx
@@ -1886,7 +1886,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U36"/>
+  <dimension ref="A1:U37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20.7109375" customWidth="1" style="7" min="1" max="21"/>
@@ -4950,6 +4950,85 @@
         </is>
       </c>
       <c r="U36" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>CDISCPILOT01</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>GUARD-SINGLE</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>DIABP</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Diastolic Blood Pressure</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>STANDING</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>71</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>mmHg</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>SCREENING 1</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>SCREENING</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>2012-11-23</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>-7</v>
       </c>
     </row>
